--- a/public/modelos/PCMD-05-Ficha-Falha.xlsx
+++ b/public/modelos/PCMD-05-Ficha-Falha.xlsx
@@ -538,7 +538,7 @@
       <row>0</row>
       <rowOff>228600</rowOff>
     </from>
-    <ext cx="1628775" cy="371475"/>
+    <ext cx="1283467" cy="371475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -568,7 +568,7 @@
       <row>0</row>
       <rowOff>247650</rowOff>
     </from>
-    <ext cx="1495425" cy="342900"/>
+    <ext cx="1184739" cy="342900"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -598,7 +598,7 @@
       <row>0</row>
       <rowOff>142875</rowOff>
     </from>
-    <ext cx="2362200" cy="542925"/>
+    <ext cx="1875836" cy="542925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
